--- a/Extra/Phân công.xlsx
+++ b/Extra/Phân công.xlsx
@@ -1,13 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\012012301310_Group04_UDM09\Extra\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A8B755-F8B6-4B8E-94E5-79D377EA0E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="test" sheetId="1" r:id="rId1"/>
+    <sheet name="Proof" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -18,23 +25,423 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="127">
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Input/Scenario</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>Test Result</t>
+  </si>
+  <si>
+    <t>Proof</t>
+  </si>
+  <si>
+    <t>TC_1</t>
+  </si>
+  <si>
+    <t>test_identity.py</t>
+  </si>
+  <si>
+    <t>PeerID Generate</t>
+  </si>
+  <si>
+    <t>Tạo PeerID mới</t>
+  </si>
+  <si>
+    <t>PeerID được tạo thành công</t>
+  </si>
+  <si>
+    <t>pass</t>
+  </si>
+  <si>
+    <t>TC_2</t>
+  </si>
+  <si>
+    <t>PeerID Save</t>
+  </si>
+  <si>
+    <t>Lưu PeerID xuống file</t>
+  </si>
+  <si>
+    <t>File được tạo</t>
+  </si>
+  <si>
+    <t>TC_3</t>
+  </si>
+  <si>
+    <t>PeerID Load</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load PeerID từ file </t>
+  </si>
+  <si>
+    <t>Đọc đúng dữ liệu</t>
+  </si>
+  <si>
+    <t>TC_4</t>
+  </si>
+  <si>
+    <t>test_crypto.py</t>
+  </si>
+  <si>
+    <t>Fernet Key Generate</t>
+  </si>
+  <si>
+    <t>Sinh khóa mã hóa</t>
+  </si>
+  <si>
+    <t>Key hợp lệ</t>
+  </si>
+  <si>
+    <t>TC_5</t>
+  </si>
+  <si>
+    <t>Encrypt Message</t>
+  </si>
+  <si>
+    <t>Mã hóa tin nhắn</t>
+  </si>
+  <si>
+    <t>Sinh ciphertext</t>
+  </si>
+  <si>
+    <t>TC_6</t>
+  </si>
+  <si>
+    <t>Decrypt Message</t>
+  </si>
+  <si>
+    <t>Giải mã ciphertext</t>
+  </si>
+  <si>
+    <t>Khôi phục dữ liệu gốc</t>
+  </si>
+  <si>
+    <t>TC_7</t>
+  </si>
+  <si>
+    <t>Invalid Token</t>
+  </si>
+  <si>
+    <t>Giải mã token</t>
+  </si>
+  <si>
+    <t>Bắt exception</t>
+  </si>
+  <si>
+    <t>TC_8</t>
+  </si>
+  <si>
+    <t>test_rsa.py</t>
+  </si>
+  <si>
+    <t>RSA Key Pair</t>
+  </si>
+  <si>
+    <t>Sinh cặp khóa RSA</t>
+  </si>
+  <si>
+    <t>Public/Private tạo thành công</t>
+  </si>
+  <si>
+    <t>TC_9</t>
+  </si>
+  <si>
+    <t>RSA Encrypt</t>
+  </si>
+  <si>
+    <t>Mã khóa bằng Public Key</t>
+  </si>
+  <si>
+    <t>Ciphertext sinh ra</t>
+  </si>
+  <si>
+    <t>TC_10</t>
+  </si>
+  <si>
+    <t>RSA Decrypt</t>
+  </si>
+  <si>
+    <t>Giải mã bằng Private Key</t>
+  </si>
+  <si>
+    <t>Dữ liệu đúng</t>
+  </si>
+  <si>
+    <t>TC_11</t>
+  </si>
+  <si>
+    <t>test_jwt.py</t>
+  </si>
+  <si>
+    <t>JWT Generate</t>
+  </si>
+  <si>
+    <t>Tạo JWT token</t>
+  </si>
+  <si>
+    <t>Token được sinh thành công</t>
+  </si>
+  <si>
+    <t>TC_12</t>
+  </si>
+  <si>
+    <t>JWT Verify</t>
+  </si>
+  <si>
+    <t>Xác thực JWT token</t>
+  </si>
+  <si>
+    <t>Token hợp lệ</t>
+  </si>
+  <si>
+    <t>TC_13</t>
+  </si>
+  <si>
+    <t>test_tofu</t>
+  </si>
+  <si>
+    <t>Fingerprint Verify</t>
+  </si>
+  <si>
+    <t>So khớp fingerprint</t>
+  </si>
+  <si>
+    <t>Verified</t>
+  </si>
+  <si>
+    <t>TC_14</t>
+  </si>
+  <si>
+    <t>test_trust_store.py</t>
+  </si>
+  <si>
+    <t>Trust Store Save/Load</t>
+  </si>
+  <si>
+    <t>Lưu và đọc thông tin trust</t>
+  </si>
+  <si>
+    <t>Dữ liệu được khôi phục đúng</t>
+  </si>
+  <si>
+    <t>TC_15</t>
+  </si>
+  <si>
+    <t>test_contact_book.py</t>
+  </si>
+  <si>
+    <t>Contact Add</t>
+  </si>
+  <si>
+    <t>Thêm contact mới</t>
+  </si>
+  <si>
+    <t>Contact lưu thành công</t>
+  </si>
+  <si>
+    <t>TC_16</t>
+  </si>
+  <si>
+    <t>Contact search</t>
+  </si>
+  <si>
+    <t>Tìm kiếm contact</t>
+  </si>
+  <si>
+    <t>Trả về đúng kết quả</t>
+  </si>
+  <si>
+    <t>TC_17</t>
+  </si>
+  <si>
+    <t>Contact remove</t>
+  </si>
+  <si>
+    <t>Xóa contact</t>
+  </si>
+  <si>
+    <t>Contact bị xóa</t>
+  </si>
+  <si>
+    <t>TC_18</t>
+  </si>
+  <si>
+    <t>test_history.py</t>
+  </si>
+  <si>
+    <t>Message History</t>
+  </si>
+  <si>
+    <t>Lưu lịch sử chat</t>
+  </si>
+  <si>
+    <t>Tin nhắn được lưu</t>
+  </si>
+  <si>
+    <t>TC_19</t>
+  </si>
+  <si>
+    <t>test_protocol.py</t>
+  </si>
+  <si>
+    <t>Packet Encode</t>
+  </si>
+  <si>
+    <t>Tạo packet gửi mạng</t>
+  </si>
+  <si>
+    <t>Pecket hợp lệ</t>
+  </si>
+  <si>
+    <t>TC_20</t>
+  </si>
+  <si>
+    <t>Packet Decode</t>
+  </si>
+  <si>
+    <t>Giải mã packet nhận được</t>
+  </si>
+  <si>
+    <t>Dữ liệu khôi phục đúng</t>
+  </si>
+  <si>
+    <t>TC_21</t>
+  </si>
+  <si>
+    <t>test_node.py</t>
+  </si>
+  <si>
+    <t>Peer Connection</t>
+  </si>
+  <si>
+    <t>Kết nối giữa các peer</t>
+  </si>
+  <si>
+    <t>Kết nối thành công</t>
+  </si>
+  <si>
+    <t>TC_22</t>
+  </si>
+  <si>
+    <t>Message Exchange</t>
+  </si>
+  <si>
+    <t>Gửi và nhận tin nhắn</t>
+  </si>
+  <si>
+    <t>Tin nhắn truyền thành công</t>
+  </si>
+  <si>
+    <t>TC_23</t>
+  </si>
+  <si>
+    <t>test_storage_manager.py</t>
+  </si>
+  <si>
+    <t>Storage Save/Load</t>
+  </si>
+  <si>
+    <t>Lưu và đọc dữ liệu</t>
+  </si>
+  <si>
+    <t>Dữ liệu luôn đúng</t>
+  </si>
+  <si>
+    <t>TC_24</t>
+  </si>
+  <si>
+    <t>test_discovery.py</t>
+  </si>
+  <si>
+    <t>Peer Discovery</t>
+  </si>
+  <si>
+    <t>Tìm kiếm peer trong mạng</t>
+  </si>
+  <si>
+    <t>Không lẫn dữ liệu</t>
+  </si>
+  <si>
+    <t>TC_25</t>
+  </si>
+  <si>
+    <t>test_discovery_socket.py</t>
+  </si>
+  <si>
+    <t>Discovery Broadcast</t>
+  </si>
+  <si>
+    <t>Gửi gói broadcast discovery</t>
+  </si>
+  <si>
+    <t>Peer nhận được broadcast</t>
+  </si>
+  <si>
+    <t>TC_04</t>
+  </si>
+  <si>
+    <t>TC_05</t>
+  </si>
+  <si>
+    <t>TC_06</t>
+  </si>
+  <si>
+    <t>TC_07</t>
+  </si>
+  <si>
+    <t>TC_08</t>
+  </si>
+  <si>
+    <t>TC_09</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="163"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,11 +456,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -66,6 +495,818 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>579121</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Hình ảnh 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F958BF4D-DADB-43F6-B31B-32215D3DCD1F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11399521" y="403860"/>
+          <a:ext cx="3931920" cy="678180"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>556260</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>68581</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Hình ảnh 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73B5B2EA-E3CC-49AF-B991-825D8B466B7B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11399520" y="1089661"/>
+          <a:ext cx="3909060" cy="944880"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>7621</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>579120</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>30481</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Hình ảnh 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDA6D011-C62A-41ED-A57E-B7DAF47D8123}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11422380" y="2011681"/>
+          <a:ext cx="3909060" cy="723900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>579120</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>129541</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Hình ảnh 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0624FEC-0E02-410E-9CC1-0F8D3E6F0FFC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11399520" y="2689861"/>
+          <a:ext cx="3931920" cy="480060"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>579120</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="Hình ảnh 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0EAFDED2-5F46-4248-929B-D052C0907613}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2011680" y="350520"/>
+          <a:ext cx="3931920" cy="883920"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>556260</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="Hình ảnh 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17CE7618-D3CB-47A2-A41C-D7608899FBB7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2011680" y="1577340"/>
+          <a:ext cx="3909060" cy="944880"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>556260</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="Hình ảnh 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B38745AA-2AF2-49C6-9983-A3EC41DCE0C2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2011680" y="2628900"/>
+          <a:ext cx="3909060" cy="723900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>579120</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="Hình ảnh 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1FBE116-1843-431E-82CE-3D93921C50B6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2011680" y="3505200"/>
+          <a:ext cx="3931920" cy="480060"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>586741</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>99681</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="Hình ảnh 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8947C26A-F25C-4201-A722-27832F60D759}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2011681" y="4030981"/>
+          <a:ext cx="3939540" cy="800720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>594360</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>9063</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="Hình ảnh 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84C1D235-816D-467E-AB40-BC9128F62147}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2011681" y="4907280"/>
+          <a:ext cx="3947159" cy="710103"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>563880</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>73727</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="25" name="Hình ảnh 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63779876-9942-4C94-9598-E5CDF2650B79}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2011680" y="5783580"/>
+          <a:ext cx="3916680" cy="774767"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>579121</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>117061</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="26" name="Hình ảnh 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC641C4F-22F9-4615-8E7A-6569CB350320}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2011681" y="6835141"/>
+          <a:ext cx="3931920" cy="467580"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>162448</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="27" name="Hình ảnh 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB6A455A-1173-4E56-9FFA-99B1C17857C7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2011680" y="7536180"/>
+          <a:ext cx="4251960" cy="2791348"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>297180</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>32531</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="28" name="Hình ảnh 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07BA17D1-1755-4EB2-9B17-BD8CAF446C26}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2011680" y="10515601"/>
+          <a:ext cx="4320540" cy="1259350"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>167640</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>149278</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="29" name="Hình ảnh 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D677781B-6AC2-44C9-8EF5-448E3E34D5EF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2011681" y="12092941"/>
+          <a:ext cx="4190999" cy="499797"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>198120</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>171415</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="30" name="Hình ảnh 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E40DCE38-07B4-498E-ABD9-6ECA357E8500}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2011680" y="12793980"/>
+          <a:ext cx="4221480" cy="697195"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>308156</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>99061</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="31" name="Hình ảnh 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7ED9742E-DC04-4FFB-A9F2-EA2B620FFC93}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2011680" y="13670281"/>
+          <a:ext cx="4331516" cy="1150620"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -330,10 +1571,790 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="C2:I28"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="24.296875" customWidth="1"/>
+    <col min="5" max="5" width="27.5" customWidth="1"/>
+    <col min="6" max="6" width="23.5" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="C2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="3:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="C3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="7"/>
+    </row>
+    <row r="4" spans="3:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="C4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="7"/>
+    </row>
+    <row r="5" spans="3:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="C5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="7"/>
+    </row>
+    <row r="6" spans="3:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="C6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="7"/>
+    </row>
+    <row r="7" spans="3:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="C7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="7"/>
+    </row>
+    <row r="8" spans="3:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="C8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="7"/>
+    </row>
+    <row r="9" spans="3:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="C9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" s="7"/>
+    </row>
+    <row r="10" spans="3:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="C10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="7"/>
+    </row>
+    <row r="11" spans="3:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="C11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="7"/>
+    </row>
+    <row r="12" spans="3:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="C12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I12" s="7"/>
+    </row>
+    <row r="13" spans="3:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="C13" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13" s="7"/>
+    </row>
+    <row r="14" spans="3:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="C14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I14" s="7"/>
+    </row>
+    <row r="15" spans="3:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="C15" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I15" s="6"/>
+    </row>
+    <row r="16" spans="3:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="C16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16" t="s">
+        <v>67</v>
+      </c>
+      <c r="F16" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I16" s="6"/>
+    </row>
+    <row r="17" spans="3:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="C17" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I17" s="6"/>
+    </row>
+    <row r="18" spans="3:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="C18" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I18" s="6"/>
+    </row>
+    <row r="19" spans="3:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="C19" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I19" s="6"/>
+    </row>
+    <row r="20" spans="3:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="C20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I20" s="6"/>
+    </row>
+    <row r="21" spans="3:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="C21" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I21" s="6"/>
+    </row>
+    <row r="22" spans="3:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="C22" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" t="s">
+        <v>94</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I22" s="6"/>
+    </row>
+    <row r="23" spans="3:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="C23" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I23" s="6"/>
+    </row>
+    <row r="24" spans="3:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="C24" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I24" s="6"/>
+    </row>
+    <row r="25" spans="3:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="C25" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I25" s="6"/>
+    </row>
+    <row r="26" spans="3:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="C26" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I26" s="6"/>
+    </row>
+    <row r="27" spans="3:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="C27" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I27" s="6"/>
+    </row>
+    <row r="28" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="I10:I12"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="I3:I5"/>
+    <mergeCell ref="I6:I9"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72E8E1B3-FA13-4FF3-8483-930545D34C56}">
+  <dimension ref="C3:D85"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="3" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="8"/>
+    </row>
+    <row r="5" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="8"/>
+    </row>
+    <row r="6" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="8"/>
+    </row>
+    <row r="10" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D10" s="8"/>
+    </row>
+    <row r="11" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>122</v>
+      </c>
+      <c r="D11" s="8"/>
+    </row>
+    <row r="12" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>123</v>
+      </c>
+      <c r="D12" s="8"/>
+    </row>
+    <row r="13" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>124</v>
+      </c>
+      <c r="D13" s="8"/>
+    </row>
+    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>125</v>
+      </c>
+      <c r="D17" s="8"/>
+    </row>
+    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
+        <v>126</v>
+      </c>
+      <c r="D18" s="8"/>
+    </row>
+    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="8"/>
+    </row>
+    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D20" s="8"/>
+    </row>
+    <row r="22" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="8"/>
+    </row>
+    <row r="23" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="8"/>
+    </row>
+    <row r="25" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C25" t="s">
+        <v>60</v>
+      </c>
+      <c r="D25" s="8"/>
+    </row>
+    <row r="26" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D26" s="8"/>
+    </row>
+    <row r="27" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D27" s="8"/>
+    </row>
+    <row r="28" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D28" s="8"/>
+    </row>
+    <row r="30" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C30" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="35" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C35" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35" s="8"/>
+    </row>
+    <row r="36" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C36" t="s">
+        <v>75</v>
+      </c>
+      <c r="D36" s="8"/>
+    </row>
+    <row r="37" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C37" t="s">
+        <v>79</v>
+      </c>
+      <c r="D37" s="8"/>
+    </row>
+    <row r="41" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C41" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="45" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C45" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="46" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C46" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="62" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C62" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="63" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C63" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="71" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C71" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="75" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C75" t="s">
+        <v>111</v>
+      </c>
+      <c r="D75" s="8"/>
+    </row>
+    <row r="76" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D76" s="8"/>
+    </row>
+    <row r="77" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D77" s="8"/>
+    </row>
+    <row r="78" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D78" s="8"/>
+    </row>
+    <row r="80" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C80" t="s">
+        <v>116</v>
+      </c>
+      <c r="D80" s="8"/>
+    </row>
+    <row r="81" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D81" s="8"/>
+    </row>
+    <row r="82" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D82" s="8"/>
+    </row>
+    <row r="83" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D83" s="8"/>
+    </row>
+    <row r="84" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D84" s="8"/>
+    </row>
+    <row r="85" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D85" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="D25:D28"/>
+    <mergeCell ref="D35:D37"/>
+    <mergeCell ref="D75:D78"/>
+    <mergeCell ref="D80:D85"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="D10:D13"/>
+    <mergeCell ref="D17:D20"/>
+    <mergeCell ref="D22:D23"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Extra/Phân công.xlsx
+++ b/Extra/Phân công.xlsx
@@ -1,26 +1,214 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07c1b08ee16acfbd/Tài liệu/UTH (ws)/LapTrinhMang/012012301310_Group04_UDM09/Extra/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3B14E54-2BBE-4D7A-9844-D4EB0D2C286D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Phân công Nhiệm vụ" sheetId="1" r:id="rId1"/>
+    <sheet name="Lộ trình Tích hợp" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+  <si>
+    <t>MSSV</t>
+  </si>
+  <si>
+    <t>Họ tên</t>
+  </si>
+  <si>
+    <t>Vai trò / Module</t>
+  </si>
+  <si>
+    <t>Files Phụ trách</t>
+  </si>
+  <si>
+    <t>Nhiệm vụ Cốt lõi</t>
+  </si>
+  <si>
+    <t>Hướng dẫn Triển khai &amp; Ràng buộc Kỹ thuật</t>
+  </si>
+  <si>
+    <t>Đánh đổi &amp; Rủi ro</t>
+  </si>
+  <si>
+    <t>089205009200</t>
+  </si>
+  <si>
+    <t>Trần Hữu Tài</t>
+  </si>
+  <si>
+    <t>Core Network, Vòng đời Ứng dụng &amp; Cấu hình</t>
+  </si>
+  <si>
+    <t>network/node.py, network/discovery.py, network/validation.py, main.py, config.py</t>
+  </si>
+  <si>
+    <t>Quản lý entry-point (main.py) và cấu hình toàn cục. Triển khai TCP Server đa luồng và cơ chế UDP Broadcast Discovery. Xử lý các edge-case về mạng.</t>
+  </si>
+  <si>
+    <t>1. Quản lý tài nguyên: Đảm bảo socket luôn được đóng thông qua khối finally hoặc context manager để tránh rò rỉ file descriptor.
+2. Đồng bộ hóa: Mọi truy cập vào dictionary quản lý session (peers) phải bọc trong threading.Lock().
+3. Tham số mạng: config.py phải là nguồn tham chiếu duy nhất (Single Source of Truth) cho các hằng số mạng (PORT, TIMEOUT, MAX_SIZE).</t>
+  </si>
+  <si>
+    <t>UDP Broadcast không định tuyến qua được NAT/Subnet khác. Giới hạn MAX_PACKET_SIZE tĩnh trong config yêu cầu mọi luồng phía trên không được gửi gói tin vượt kích thước.</t>
+  </si>
+  <si>
+    <t>052206013184</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn Tài</t>
+  </si>
+  <si>
+    <t>Bảo mật (Security), Định danh (Identity) &amp; Mã hóa</t>
+  </si>
+  <si>
+    <t>identity/identity_manager.py, security/crypto.py, security/jwt_handler.py, security/rsa_utils.py</t>
+  </si>
+  <si>
+    <t>Xây dựng hạ tầng khóa công khai (PKI) cục bộ bằng RSA-2048. Sinh mã định danh (Peer ID) từ hàm băm SHA-256. Đóng gói JWT và mã hóa đường truyền bằng Fernet.</t>
+  </si>
+  <si>
+    <t>1. Peer ID: Bắt buộc sinh từ bản băm SHA-256 của chuỗi PEM (cả header) để đảm bảo tính duy nhất và không thể giả mạo.
+2. Tối ưu hiệu năng: Cache JWT Token tối đa theo thời gian JWT_EXPIRE_HOURS để tránh chi phí ký RSA liên tục cho mỗi gói UDP broadcast.
+3. Quản lý Session Key: Fernet là mã hóa đối xứng, khâu trao đổi khóa ban đầu qua TCP Handshake phải xác thực nghiêm ngặt.</t>
+  </si>
+  <si>
+    <t>Sử dụng Fernet thay cho mTLS/TLS gốc giúp dễ quản lý ở cấp độ ứng dụng nhưng sẽ mất đi các cơ sở bảo mật ở tầng Transport. Cần bắt chặt ngoại lệ InvalidToken.</t>
+  </si>
+  <si>
+    <t>052206003938</t>
+  </si>
+  <si>
+    <t>Nguyễn Phan Hoài Bình</t>
+  </si>
+  <si>
+    <t>Giao thức (Protocol) &amp; Quản lý Truyền tải File</t>
+  </si>
+  <si>
+    <t>message/protocol.py, network/transfer_manager.py</t>
+  </si>
+  <si>
+    <t>Định nghĩa format khung truyền (4-byte length + JSON payload). Xử lý truyền file dung lượng lớn thông qua kỹ thuật chia nhỏ (chunking) và mã hóa từng phần.</t>
+  </si>
+  <si>
+    <t>1. Tránh tràn RAM: Tuyệt đối không đọc toàn bộ file vào bộ nhớ. Đọc theo chunk (FILE_CHUNK_SIZE), mã hóa và truyền đi.
+2. Toàn vẹn dữ liệu: Tính toán SHA-256 rolling cho từng chunk được đọc/ghi để đối chiếu ở gói FILE_COMPLETE cuối cùng.
+3. Mã hóa Base64: Payload của file chunk phải được bọc qua Base64 trước khi gài vào JSON.</t>
+  </si>
+  <si>
+    <t>Việc encode file nhị phân sang Base64 rồi bọc JSON làm tăng overhead khoảng 33% băng thông mạng. Đổi lại, kiến trúc giao thức được chuẩn hóa duy nhất một luồng xử lý chuỗi.</t>
+  </si>
+  <si>
+    <t>080306012851</t>
+  </si>
+  <si>
+    <t>Lưu trữ (Storage) &amp; Cơ chế Trust-On-First-Use (TOFU)</t>
+  </si>
+  <si>
+    <t>storage/storage_manager.py, storage/contact_book.py, storage/message_history.py, trust/tofu_engine.py, trust/trust_store.py, trust/trust_state.py</t>
+  </si>
+  <si>
+    <t>Quản lý cơ sở dữ liệu cục bộ dựa trên JSON (danh bạ, lịch sử tin nhắn). Triển khai máy trạng thái TOFU (NEW, TRUSTED, VERIFIED, MISMATCH, BLOCKED) để phòng chống MITM.</t>
+  </si>
+  <si>
+    <t>082206002652</t>
+  </si>
+  <si>
+    <t>Lê Quốc Thịnh</t>
+  </si>
+  <si>
+    <t>Giao diện (GUI Layer) &amp; Controller</t>
+  </si>
+  <si>
+    <t>controllers/controller.py, gui/app.py, gui/main_window.py, gui/sidebar.py, gui/chatbox.py, gui/chat_bubble.py, gui/peer_details.py, gui/transfer_panel.py, gui/trust_dialog.py, gui/statusbar.py, gui/theme.py, gui/ui_state.py</t>
+  </si>
+  <si>
+    <t>Xây dựng Adapter Pattern (Controller) nối tầng Mạng với tầng View. Thiết kế UI bằng CustomTkinter đảm bảo responsive và luồng sự kiện phi đồng bộ mượt mà.</t>
+  </si>
+  <si>
+    <t>CustomTkinter không hỗ trợ tốt việc cập nhật quá thường xuyên (như progress bar của file truyền ở tốc độ cao). Cần throttle/debounce các tín hiệu update giao diện để tránh làm nghẽn (freeze) Event Loop.</t>
+  </si>
+  <si>
+    <t>Giai đoạn</t>
+  </si>
+  <si>
+    <t>Công việc</t>
+  </si>
+  <si>
+    <t>Mục tiêu Kiểm thử</t>
+  </si>
+  <si>
+    <t>Phase 1: Bootstrapping &amp; Identity</t>
+  </si>
+  <si>
+    <t>Khởi chạy main.py, sinh RSA/Peer_ID (identity_manager.py), lưu thông số tĩnh (config.py).</t>
+  </si>
+  <si>
+    <t>File key được ghi xuống đĩa, băm SHA-256 đúng, Peer ID cố định qua nhiều lần chạy.</t>
+  </si>
+  <si>
+    <t>Phase 2: Networking &amp; Protocol</t>
+  </si>
+  <si>
+    <t>Xây dựng luồng Node TCP, UDP Broadcast, định dạng khung tin nhắn (protocol.py).</t>
+  </si>
+  <si>
+    <t>Kết nối 2 Node thành công, gói handshake đi qua đủ 4-byte header không bị cắt xén.</t>
+  </si>
+  <si>
+    <t>Phase 3: Storage, Trust &amp; Transfer</t>
+  </si>
+  <si>
+    <t>Lưu lịch sử tin nhắn. Khởi động TOFU engine. Tiến hành mã hóa Base64 và cắt chunk để gửi file.</t>
+  </si>
+  <si>
+    <t>Phát hiện được Fingerprint thay đổi (MISMATCH). File gửi qua khớp mã băm gốc.</t>
+  </si>
+  <si>
+    <t>Phase 4: Controller &amp; GUI</t>
+  </si>
+  <si>
+    <t>Đẩy state lên giao diện qua controller.py, xử lý Trust Dialog, hiện Progress bar khi tải file.</t>
+  </si>
+  <si>
+    <t>App không bị 'Not Responding', giao diện hiển thị đúng trạng thái Trust (màu sắc).</t>
+  </si>
+  <si>
+    <t>1. Ghi tệp an toàn (Atomic Write): Việc ghi JSON phải thực hiện ra file .tmp trước rồi mới rename đè lên file chính, chống hỏng file khi sập nguồn.
+2. Thread-safety: Dùng threading.RLock() cho trust_store và message_history vì nhiều luồng nhận tin nhắn có thể truy cập cùng lúc.
+3. State Machine: Không tự động chuyển đổi trạng thái từ MISMATCH sang TRUSTED nếu chưa có xác nhận từ người dùng.</t>
+  </si>
+  <si>
+    <t>Kiến trúc JSON phẳng cho từng peer_id có độ phức tạp ghi là O(n) do phải load và dump lại toàn bộ mảng tin nhắn mỗi lần append. Tuy nhiên, nó đạt được tính cô lập lỗi (fault isolation) rất cao.</t>
+  </si>
+  <si>
+    <t>1. Main Thread Rule: Tuyệt đối không thay đổi thuộc tính UI từ luồng socket. Phải sử dụng after() của Tkinter hoặc Message Queue để đẩy sự kiện cập nhật giao diện.
+2. UI State: Các module GUI chỉ được đọc dữ liệu từ ui_state.py để đảm bảo tính nhất quán (Single Source of Truth) thay vì tự giữ state riêng.
+3. Ràng buộc resize: Cập nhật biến wraplength trong chat_bubble.py thông qua event &lt;Configure&gt; của cột hiển thị.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trần Thị Thanh Thơ </t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +216,47 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FFF9FAFB"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FAFB"/>
+        <bgColor rgb="FFF9FAFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor rgb="FF1F2937"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,18 +264,53 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -79,44 +333,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -143,15 +397,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -178,7 +431,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -190,150 +442,393 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.77734375" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="40" style="1" customWidth="1"/>
+    <col min="7" max="7" width="39.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="184.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="218.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="184.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="218.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="35.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="50.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="50.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="50.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="50.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Extra/Phân công.xlsx
+++ b/Extra/Phân công.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07c1b08ee16acfbd/Tài liệu/UTH (ws)/LapTrinhMang/012012301310_Group04_UDM09/Extra/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nguye\012012301310_Group04_UDM09\Extra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3B14E54-2BBE-4D7A-9844-D4EB0D2C286D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E90C2D68-8934-4DFD-95E2-6FA8CF8F7186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -93,9 +93,6 @@
     <t>052206003938</t>
   </si>
   <si>
-    <t>Nguyễn Phan Hoài Bình</t>
-  </si>
-  <si>
     <t>Giao thức (Protocol) &amp; Quản lý Truyền tải File</t>
   </si>
   <si>
@@ -202,6 +199,9 @@
   </si>
   <si>
     <t xml:space="preserve">Trần Thị Thanh Thơ </t>
+  </si>
+  <si>
+    <t>Nguyễn Phan Hoài Bin</t>
   </si>
 </sst>
 </file>
@@ -693,68 +693,68 @@
         <v>21</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="C5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="F5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="218.4" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -775,57 +775,57 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C1" s="8" t="s">
         <v>39</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="50.4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="50.4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="50.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="50.4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
